--- a/02_Glider_Design/C_results/weight_sweep_top_rerun.xlsx
+++ b/02_Glider_Design/C_results/weight_sweep_top_rerun.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>f23b30e</t>
+          <t>93578c8-dirty</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-28T21:48:41.719616+00:00</t>
+          <t>2026-03-31T09:54:00.092050+00:00</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
     </row>
     <row r="74">
@@ -2627,10 +2627,10 @@
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7215140017787486</v>
+        <v>0.7208494626215385</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.7852675969908308</v>
+        <v>0.8167931169621288</v>
       </c>
       <c r="R2" t="n">
         <v>1.040282834249715</v>
@@ -2663,7 +2663,7 @@
         <v>-1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.7852675969908308</v>
+        <v>0.8167931169621288</v>
       </c>
       <c r="AC2" t="n">
         <v>0.7615699665062574</v>
@@ -2740,10 +2740,10 @@
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>0.722144254254269</v>
+        <v>0.7212198532620753</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7835893426482706</v>
+        <v>0.8131152292092879</v>
       </c>
       <c r="R3" t="n">
         <v>2.166267395045595</v>
@@ -2776,7 +2776,7 @@
         <v>-1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.7835893426482706</v>
+        <v>0.8131152292092879</v>
       </c>
       <c r="AC3" t="n">
         <v>0.7615699665258173</v>
@@ -2853,10 +2853,10 @@
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7218247071237285</v>
+        <v>0.7212002056733996</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.7859105538692953</v>
+        <v>0.8177328782150537</v>
       </c>
       <c r="R4" t="n">
         <v>15.08876454739261</v>
@@ -2889,7 +2889,7 @@
         <v>-1</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7859105538692953</v>
+        <v>0.8177328782150537</v>
       </c>
       <c r="AC4" t="n">
         <v>0.7615699665295264</v>
@@ -2930,7 +2930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2971,40 +2971,50 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>nom_sink_tail_mean_k</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>nom_sink_cvar_20</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>rerun_rank</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>source_sweep_run_index</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>objective_weight_w_sink</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>objective_weight_w_mass</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>objective_weight_w_trim_effort</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>objective_weight_w_wing_deflection</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>objective_weight_w_htail_deflection</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>objective_weight_w_roll_tau</t>
         </is>
@@ -3030,28 +3040,30 @@
         <v>0</v>
       </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
         <v>5</v>
       </c>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
         <v>0.2638306073747891</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>18.67856203578664</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>0.02397098387411416</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>0.03383814025109462</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>0.0216570995576821</v>
       </c>
     </row>
@@ -3075,28 +3087,30 @@
         <v>0</v>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
         <v>5</v>
       </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
         <v>0.2638306073747891</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>18.67856203578664</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>0.02397098387411416</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>0.03383814025109462</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>0.0216570995576821</v>
       </c>
     </row>
@@ -3120,28 +3134,30 @@
         <v>0</v>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
         <v>5</v>
       </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
         <v>0.2638306073747891</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>18.67856203578664</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>0.02397098387411416</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>0.03383814025109462</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>0.0216570995576821</v>
       </c>
     </row>
@@ -3168,27 +3184,33 @@
         <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0.9718481752345759</v>
       </c>
       <c r="I5" t="n">
+        <v>0.9718481752345759</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
         <v>5</v>
       </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
         <v>0.2638306073747891</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>18.67856203578664</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>0.02397098387411416</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>0.03383814025109462</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>0.0216570995576821</v>
       </c>
     </row>
@@ -3212,28 +3234,30 @@
         <v>0</v>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
         <v>5</v>
       </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
         <v>0.2638306073747891</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>18.67856203578664</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>0.02397098387411416</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>0.03383814025109462</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>0.0216570995576821</v>
       </c>
     </row>
@@ -3260,27 +3284,33 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0.8167931169621288</v>
       </c>
       <c r="I7" t="n">
+        <v>0.8167931169621288</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
         <v>5</v>
       </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
         <v>0.2638306073747891</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>18.67856203578664</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>0.02397098387411416</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>0.03383814025109462</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>0.0216570995576821</v>
       </c>
     </row>
@@ -3304,28 +3334,30 @@
         <v>0</v>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="n">
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="n">
         <v>2</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>27</v>
       </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
         <v>0.04698862362078716</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>0.01325917124942102</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>2.151606933843013</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>0.0783091834800308</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>0.2470733791131532</v>
       </c>
     </row>
@@ -3352,27 +3384,33 @@
         <v>2</v>
       </c>
       <c r="H9" t="n">
+        <v>0.8387444989570139</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.8387444989570139</v>
+      </c>
+      <c r="J9" t="n">
         <v>2</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>27</v>
       </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
         <v>0.04698862362078716</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>0.01325917124942102</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>2.151606933843013</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>0.0783091834800308</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>0.2470733791131532</v>
       </c>
     </row>
@@ -3399,27 +3437,33 @@
         <v>1</v>
       </c>
       <c r="H10" t="n">
+        <v>0.8131152292092879</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.8131152292092879</v>
+      </c>
+      <c r="J10" t="n">
         <v>2</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>27</v>
       </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
         <v>0.04698862362078716</v>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
         <v>0.01325917124942102</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>2.151606933843013</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>0.0783091834800308</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>0.2470733791131532</v>
       </c>
     </row>
@@ -3443,28 +3487,30 @@
         <v>0</v>
       </c>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="n">
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="n">
         <v>2</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>27</v>
       </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
         <v>0.04698862362078716</v>
       </c>
-      <c r="L11" t="n">
+      <c r="N11" t="n">
         <v>0.01325917124942102</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>2.151606933843013</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>0.0783091834800308</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>0.2470733791131532</v>
       </c>
     </row>
@@ -3488,28 +3534,30 @@
         <v>0</v>
       </c>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="n">
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="n">
         <v>2</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>27</v>
       </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
         <v>0.04698862362078716</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>0.01325917124942102</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>2.151606933843013</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>0.0783091834800308</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>0.2470733791131532</v>
       </c>
     </row>
@@ -3533,28 +3581,30 @@
         <v>0</v>
       </c>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="n">
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="n">
         <v>2</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>27</v>
       </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
         <v>0.04698862362078716</v>
       </c>
-      <c r="L13" t="n">
+      <c r="N13" t="n">
         <v>0.01325917124942102</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>2.151606933843013</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>0.0783091834800308</v>
       </c>
-      <c r="O13" t="n">
+      <c r="Q13" t="n">
         <v>0.2470733791131532</v>
       </c>
     </row>
@@ -3578,28 +3628,30 @@
         <v>0</v>
       </c>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="n">
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="n">
         <v>3</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>29</v>
       </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
         <v>0.0260300013176861</v>
       </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
         <v>0.9334028457295769</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>22.74354390023092</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>0.3640585039483271</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
         <v>0.02867338561159859</v>
       </c>
     </row>
@@ -3623,28 +3675,30 @@
         <v>0</v>
       </c>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="n">
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="n">
         <v>3</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>29</v>
       </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
         <v>0.0260300013176861</v>
       </c>
-      <c r="L15" t="n">
+      <c r="N15" t="n">
         <v>0.9334028457295769</v>
       </c>
-      <c r="M15" t="n">
+      <c r="O15" t="n">
         <v>22.74354390023092</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>0.3640585039483271</v>
       </c>
-      <c r="O15" t="n">
+      <c r="Q15" t="n">
         <v>0.02867338561159859</v>
       </c>
     </row>
@@ -3668,28 +3722,30 @@
         <v>0</v>
       </c>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="n">
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="n">
         <v>3</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>29</v>
       </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
         <v>0.0260300013176861</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>0.9334028457295769</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>22.74354390023092</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>0.3640585039483271</v>
       </c>
-      <c r="O16" t="n">
+      <c r="Q16" t="n">
         <v>0.02867338561159859</v>
       </c>
     </row>
@@ -3713,28 +3769,30 @@
         <v>0</v>
       </c>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="n">
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="n">
         <v>3</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>29</v>
       </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
         <v>0.0260300013176861</v>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
         <v>0.9334028457295769</v>
       </c>
-      <c r="M17" t="n">
+      <c r="O17" t="n">
         <v>22.74354390023092</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>0.3640585039483271</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
         <v>0.02867338561159859</v>
       </c>
     </row>
@@ -3761,27 +3819,33 @@
         <v>1</v>
       </c>
       <c r="H18" t="n">
+        <v>0.8177328782150537</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.8177328782150537</v>
+      </c>
+      <c r="J18" t="n">
         <v>3</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>29</v>
       </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
         <v>0.0260300013176861</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>0.9334028457295769</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>22.74354390023092</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>0.3640585039483271</v>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>0.02867338561159859</v>
       </c>
     </row>
@@ -3805,28 +3869,30 @@
         <v>0</v>
       </c>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="n">
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="n">
         <v>3</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>29</v>
       </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
         <v>0.0260300013176861</v>
       </c>
-      <c r="L19" t="n">
+      <c r="N19" t="n">
         <v>0.9334028457295769</v>
       </c>
-      <c r="M19" t="n">
+      <c r="O19" t="n">
         <v>22.74354390023092</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>0.3640585039483271</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>0.02867338561159859</v>
       </c>
     </row>

--- a/02_Glider_Design/C_results/weight_sweep_top_rerun.xlsx
+++ b/02_Glider_Design/C_results/weight_sweep_top_rerun.xlsx
@@ -2930,7 +2930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3019,6 +3019,16 @@
           <t>objective_weight_w_roll_tau</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>trace_sink_tail_mean_k</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>trace_sink_cvar_20</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -3066,6 +3076,12 @@
       <c r="Q2" t="n">
         <v>0.0216570995576821</v>
       </c>
+      <c r="R2" t="n">
+        <v>0.8167931169621288</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.8167931169621288</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -3113,6 +3129,12 @@
       <c r="Q3" t="n">
         <v>0.0216570995576821</v>
       </c>
+      <c r="R3" t="n">
+        <v>0.8167931169621288</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.8167931169621288</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3160,6 +3182,12 @@
       <c r="Q4" t="n">
         <v>0.0216570995576821</v>
       </c>
+      <c r="R4" t="n">
+        <v>0.8167931169621288</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.8167931169621288</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -3212,6 +3240,12 @@
       </c>
       <c r="Q5" t="n">
         <v>0.0216570995576821</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.9718481752345759</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.9718481752345759</v>
       </c>
     </row>
     <row r="6">
@@ -3260,6 +3294,12 @@
       <c r="Q6" t="n">
         <v>0.0216570995576821</v>
       </c>
+      <c r="R6" t="n">
+        <v>0.8167931169621288</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.8167931169621288</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -3312,6 +3352,12 @@
       </c>
       <c r="Q7" t="n">
         <v>0.0216570995576821</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.8167931169621288</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.8167931169621288</v>
       </c>
     </row>
     <row r="8">
@@ -3360,6 +3406,12 @@
       <c r="Q8" t="n">
         <v>0.2470733791131532</v>
       </c>
+      <c r="R8" t="n">
+        <v>0.8131152292092879</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.8131152292092879</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -3413,6 +3465,12 @@
       <c r="Q9" t="n">
         <v>0.2470733791131532</v>
       </c>
+      <c r="R9" t="n">
+        <v>0.8387444989570139</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.8387444989570139</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -3465,6 +3523,12 @@
       </c>
       <c r="Q10" t="n">
         <v>0.2470733791131532</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.8131152292092879</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.8131152292092879</v>
       </c>
     </row>
     <row r="11">
@@ -3513,6 +3577,12 @@
       <c r="Q11" t="n">
         <v>0.2470733791131532</v>
       </c>
+      <c r="R11" t="n">
+        <v>0.8131152292092879</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.8131152292092879</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -3560,6 +3630,12 @@
       <c r="Q12" t="n">
         <v>0.2470733791131532</v>
       </c>
+      <c r="R12" t="n">
+        <v>0.8131152292092879</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.8131152292092879</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -3607,6 +3683,12 @@
       <c r="Q13" t="n">
         <v>0.2470733791131532</v>
       </c>
+      <c r="R13" t="n">
+        <v>0.8131152292092879</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.8131152292092879</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -3654,6 +3736,12 @@
       <c r="Q14" t="n">
         <v>0.02867338561159859</v>
       </c>
+      <c r="R14" t="n">
+        <v>0.8177328782150537</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.8177328782150537</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -3701,6 +3789,12 @@
       <c r="Q15" t="n">
         <v>0.02867338561159859</v>
       </c>
+      <c r="R15" t="n">
+        <v>0.8177328782150537</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.8177328782150537</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -3748,6 +3842,12 @@
       <c r="Q16" t="n">
         <v>0.02867338561159859</v>
       </c>
+      <c r="R16" t="n">
+        <v>0.8177328782150537</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.8177328782150537</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -3795,6 +3895,12 @@
       <c r="Q17" t="n">
         <v>0.02867338561159859</v>
       </c>
+      <c r="R17" t="n">
+        <v>0.8177328782150537</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.8177328782150537</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3847,6 +3953,12 @@
       </c>
       <c r="Q18" t="n">
         <v>0.02867338561159859</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.8177328782150537</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.8177328782150537</v>
       </c>
     </row>
     <row r="19">
@@ -3895,6 +4007,12 @@
       <c r="Q19" t="n">
         <v>0.02867338561159859</v>
       </c>
+      <c r="R19" t="n">
+        <v>0.8177328782150537</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.8177328782150537</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/02_Glider_Design/C_results/weight_sweep_top_rerun.xlsx
+++ b/02_Glider_Design/C_results/weight_sweep_top_rerun.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>93578c8-dirty</t>
+          <t>914634d-dirty</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-31T09:54:00.092050+00:00</t>
+          <t>2026-04-01T15:02:16.014393+00:00</t>
         </is>
       </c>
     </row>
@@ -2981,52 +2981,52 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>trace_sink_tail_mean_k</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>trace_sink_cvar_20</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>rerun_rank</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>source_sweep_run_index</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>objective_weight_w_sink</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>objective_weight_w_mass</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>objective_weight_w_trim_effort</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>objective_weight_w_wing_deflection</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>objective_weight_w_htail_deflection</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>objective_weight_w_roll_tau</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>trace_sink_tail_mean_k</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>trace_sink_cvar_20</t>
         </is>
       </c>
     </row>
@@ -3050,37 +3050,41 @@
         <v>0</v>
       </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>0.8167931090546811</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.8167931090546811</v>
+      </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0.8167931090546811</v>
       </c>
       <c r="K2" t="n">
+        <v>0.8167931090546811</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
         <v>5</v>
       </c>
-      <c r="L2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
         <v>0.2638306073747891</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>18.67856203578664</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>0.02397098387411416</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>0.03383814025109462</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>0.0216570995576821</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.8167931169621288</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.8167931169621288</v>
       </c>
     </row>
     <row r="3">
@@ -3103,37 +3107,41 @@
         <v>0</v>
       </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>0.8167930967490119</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.8167930967490119</v>
+      </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0.8167930967490119</v>
       </c>
       <c r="K3" t="n">
+        <v>0.8167930967490119</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
         <v>5</v>
       </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
         <v>0.2638306073747891</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>18.67856203578664</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>0.02397098387411416</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>0.03383814025109462</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>0.0216570995576821</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.8167931169621288</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.8167931169621288</v>
       </c>
     </row>
     <row r="4">
@@ -3156,37 +3164,41 @@
         <v>0</v>
       </c>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>0.9718481796781019</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.9718481796781019</v>
+      </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0.9718481796781019</v>
       </c>
       <c r="K4" t="n">
+        <v>0.9718481796781019</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
         <v>0.2638306073747891</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>18.67856203578664</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>0.02397098387411416</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>0.03383814025109462</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>0.0216570995576821</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.8167931169621288</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.8167931169621288</v>
       </c>
     </row>
     <row r="5">
@@ -3218,34 +3230,34 @@
         <v>0.9718481752345759</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0.9718481752345759</v>
       </c>
       <c r="K5" t="n">
+        <v>0.9718481752345759</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
         <v>5</v>
       </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
         <v>0.2638306073747891</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>18.67856203578664</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>0.02397098387411416</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>0.03383814025109462</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
         <v>0.0216570995576821</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.9718481752345759</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.9718481752345759</v>
       </c>
     </row>
     <row r="6">
@@ -3268,37 +3280,41 @@
         <v>0</v>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>0.8167931166869666</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.8167931166869666</v>
+      </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0.8167931166869666</v>
       </c>
       <c r="K6" t="n">
+        <v>0.8167931166869666</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
         <v>5</v>
       </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
         <v>0.2638306073747891</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>18.67856203578664</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>0.02397098387411416</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>0.03383814025109462</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>0.0216570995576821</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.8167931169621288</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.8167931169621288</v>
       </c>
     </row>
     <row r="7">
@@ -3330,34 +3346,34 @@
         <v>0.8167931169621288</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0.8167931169621288</v>
       </c>
       <c r="K7" t="n">
+        <v>0.8167931169621288</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
         <v>5</v>
       </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
         <v>0.2638306073747891</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>18.67856203578664</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>0.02397098387411416</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>0.03383814025109462</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>0.0216570995576821</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.8167931169621288</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.8167931169621288</v>
       </c>
     </row>
     <row r="8">
@@ -3380,37 +3396,41 @@
         <v>0</v>
       </c>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>0.8131152292084022</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.8131152292084022</v>
+      </c>
       <c r="J8" t="n">
+        <v>0.8131152292084022</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.8131152292084022</v>
+      </c>
+      <c r="L8" t="n">
         <v>2</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>27</v>
       </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
         <v>0.04698862362078716</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>0.01325917124942102</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>2.151606933843013</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>0.0783091834800308</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>0.2470733791131532</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.8131152292092879</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.8131152292092879</v>
       </c>
     </row>
     <row r="9">
@@ -3442,34 +3462,34 @@
         <v>0.8387444989570139</v>
       </c>
       <c r="J9" t="n">
+        <v>0.8387444989570139</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.8387444989570139</v>
+      </c>
+      <c r="L9" t="n">
         <v>2</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>27</v>
       </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
         <v>0.04698862362078716</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>0.01325917124942102</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>2.151606933843013</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
         <v>0.0783091834800308</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>0.2470733791131532</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.8387444989570139</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.8387444989570139</v>
       </c>
     </row>
     <row r="10">
@@ -3501,34 +3521,34 @@
         <v>0.8131152292092879</v>
       </c>
       <c r="J10" t="n">
+        <v>0.8131152292092879</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.8131152292092879</v>
+      </c>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>27</v>
       </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
         <v>0.04698862362078716</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>0.01325917124942102</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>2.151606933843013</v>
       </c>
-      <c r="P10" t="n">
+      <c r="R10" t="n">
         <v>0.0783091834800308</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
         <v>0.2470733791131532</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.8131152292092879</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.8131152292092879</v>
       </c>
     </row>
     <row r="11">
@@ -3551,37 +3571,41 @@
         <v>0</v>
       </c>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>0.8387444989552623</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.8387444989552623</v>
+      </c>
       <c r="J11" t="n">
+        <v>0.8387444989552623</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.8387444989552623</v>
+      </c>
+      <c r="L11" t="n">
         <v>2</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>27</v>
       </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
         <v>0.04698862362078716</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>0.01325917124942102</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>2.151606933843013</v>
       </c>
-      <c r="P11" t="n">
+      <c r="R11" t="n">
         <v>0.0783091834800308</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="S11" t="n">
         <v>0.2470733791131532</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.8131152292092879</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.8131152292092879</v>
       </c>
     </row>
     <row r="12">
@@ -3604,37 +3628,41 @@
         <v>0</v>
       </c>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>0.8131152296562263</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.8131152296562263</v>
+      </c>
       <c r="J12" t="n">
+        <v>0.8131152296562263</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.8131152296562263</v>
+      </c>
+      <c r="L12" t="n">
         <v>2</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>27</v>
       </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
         <v>0.04698862362078716</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>0.01325917124942102</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>2.151606933843013</v>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
         <v>0.0783091834800308</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>0.2470733791131532</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.8131152292092879</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.8131152292092879</v>
       </c>
     </row>
     <row r="13">
@@ -3657,37 +3685,41 @@
         <v>0</v>
       </c>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>0.8387444989557274</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.8387444989557274</v>
+      </c>
       <c r="J13" t="n">
+        <v>0.8387444989557274</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.8387444989557274</v>
+      </c>
+      <c r="L13" t="n">
         <v>2</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>27</v>
       </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
         <v>0.04698862362078716</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>0.01325917124942102</v>
       </c>
-      <c r="O13" t="n">
+      <c r="Q13" t="n">
         <v>2.151606933843013</v>
       </c>
-      <c r="P13" t="n">
+      <c r="R13" t="n">
         <v>0.0783091834800308</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
         <v>0.2470733791131532</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.8131152292092879</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.8131152292092879</v>
       </c>
     </row>
     <row r="14">
@@ -3710,37 +3742,41 @@
         <v>0</v>
       </c>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>0.8177328795250973</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.8177328795250973</v>
+      </c>
       <c r="J14" t="n">
+        <v>0.8177328795250973</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.8177328795250973</v>
+      </c>
+      <c r="L14" t="n">
         <v>3</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>29</v>
       </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
         <v>0.0260300013176861</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>0.9334028457295769</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
         <v>22.74354390023092</v>
       </c>
-      <c r="P14" t="n">
+      <c r="R14" t="n">
         <v>0.3640585039483271</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
         <v>0.02867338561159859</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.8177328782150537</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.8177328782150537</v>
       </c>
     </row>
     <row r="15">
@@ -3763,37 +3799,41 @@
         <v>0</v>
       </c>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>0.8177328785019731</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8177328785019731</v>
+      </c>
       <c r="J15" t="n">
+        <v>0.8177328785019731</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.8177328785019731</v>
+      </c>
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>29</v>
       </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
         <v>0.0260300013176861</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>0.9334028457295769</v>
       </c>
-      <c r="O15" t="n">
+      <c r="Q15" t="n">
         <v>22.74354390023092</v>
       </c>
-      <c r="P15" t="n">
+      <c r="R15" t="n">
         <v>0.3640585039483271</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
         <v>0.02867338561159859</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.8177328782150537</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.8177328782150537</v>
       </c>
     </row>
     <row r="16">
@@ -3816,37 +3856,41 @@
         <v>0</v>
       </c>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>0.8177328791549391</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.8177328791549391</v>
+      </c>
       <c r="J16" t="n">
+        <v>0.8177328791549391</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.8177328791549391</v>
+      </c>
+      <c r="L16" t="n">
         <v>3</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>29</v>
       </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
         <v>0.0260300013176861</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>0.9334028457295769</v>
       </c>
-      <c r="O16" t="n">
+      <c r="Q16" t="n">
         <v>22.74354390023092</v>
       </c>
-      <c r="P16" t="n">
+      <c r="R16" t="n">
         <v>0.3640585039483271</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
         <v>0.02867338561159859</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.8177328782150537</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.8177328782150537</v>
       </c>
     </row>
     <row r="17">
@@ -3869,37 +3913,41 @@
         <v>0</v>
       </c>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>0.8177328782689758</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8177328782689758</v>
+      </c>
       <c r="J17" t="n">
+        <v>0.8177328782689758</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.8177328782689758</v>
+      </c>
+      <c r="L17" t="n">
         <v>3</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>29</v>
       </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
         <v>0.0260300013176861</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>0.9334028457295769</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
         <v>22.74354390023092</v>
       </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
         <v>0.3640585039483271</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
         <v>0.02867338561159859</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.8177328782150537</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.8177328782150537</v>
       </c>
     </row>
     <row r="18">
@@ -3931,34 +3979,34 @@
         <v>0.8177328782150537</v>
       </c>
       <c r="J18" t="n">
+        <v>0.8177328782150537</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.8177328782150537</v>
+      </c>
+      <c r="L18" t="n">
         <v>3</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>29</v>
       </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
         <v>0.0260300013176861</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>0.9334028457295769</v>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>22.74354390023092</v>
       </c>
-      <c r="P18" t="n">
+      <c r="R18" t="n">
         <v>0.3640585039483271</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>0.02867338561159859</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.8177328782150537</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.8177328782150537</v>
       </c>
     </row>
     <row r="19">
@@ -3981,37 +4029,41 @@
         <v>0</v>
       </c>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>0.8177328783037147</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.8177328783037147</v>
+      </c>
       <c r="J19" t="n">
+        <v>0.8177328783037147</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.8177328783037147</v>
+      </c>
+      <c r="L19" t="n">
         <v>3</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>29</v>
       </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
         <v>0.0260300013176861</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>0.9334028457295769</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>22.74354390023092</v>
       </c>
-      <c r="P19" t="n">
+      <c r="R19" t="n">
         <v>0.3640585039483271</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="S19" t="n">
         <v>0.02867338561159859</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.8177328782150537</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.8177328782150537</v>
       </c>
     </row>
   </sheetData>

--- a/02_Glider_Design/C_results/weight_sweep_top_rerun.xlsx
+++ b/02_Glider_Design/C_results/weight_sweep_top_rerun.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>914634d-dirty</t>
+          <t>384a723-dirty</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-01T15:02:16.014393+00:00</t>
+          <t>2026-04-02T22:23:36.497347+00:00</t>
         </is>
       </c>
     </row>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -484,7 +484,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71">
@@ -1760,7 +1760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1982,25 +1982,25 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2638306073747891</v>
+        <v>0.2617924037677132</v>
       </c>
       <c r="D2" t="n">
-        <v>18.67856203578664</v>
+        <v>0.5063414494913574</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02397098387411416</v>
+        <v>0.1939218787159543</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03383814025109462</v>
+        <v>0.08419230020946894</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0216570995576821</v>
+        <v>0.6142627044519234</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -2024,46 +2024,46 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7065761983848023</v>
+        <v>0.7074074207948957</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7358996213417285</v>
+        <v>0.7358349780667149</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.040282843866633</v>
+        <v>1.253673761603159</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7615699630257173</v>
+        <v>0.7615699665150848</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1452436796411457</v>
+        <v>0.1640097423980078</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4000000107106358</v>
+        <v>0.3999999945420345</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3300424233801231</v>
+        <v>0.364382396364976</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1115526089673369</v>
+        <v>0.1185402726381636</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6684314865711555</v>
+        <v>0.6701716475842225</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1132083999413169</v>
+        <v>0.1173831996417614</v>
       </c>
       <c r="Y2" t="n">
-        <v>1886.446417239759</v>
+        <v>11091.11787807762</v>
       </c>
       <c r="Z2" t="n">
         <v>-1</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.7358996213417285</v>
+        <v>0.7358349780667149</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.7615699630257173</v>
+        <v>0.7615699665150848</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -2074,66 +2074,66 @@
         <v>1</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.6684314865711555</v>
+        <v>0.6701716475842225</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2986784091644568</v>
+        <v>0.3073002999616207</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.0003543336722753047</v>
+        <v>6.04241749976226e-05</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.01451836706531169</v>
+        <v>0.118111584264663</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.05710802689966259</v>
+        <v>0.126734732613569</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.001192220493771426</v>
+        <v>0.03129507300408594</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.040282843866633</v>
+        <v>1.253673761603159</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0.5786748227286269</v>
+        <v>-0.5820429591971319</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.271343439133855</v>
+        <v>-0.2955565194854586</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1.620314140253805</v>
+        <v>-0.7123731900467094</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1.470593513862387</v>
+        <v>-1.074727625002086</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-1.664399707010766</v>
+        <v>-0.2116458524851494</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04698862362078716</v>
+        <v>0.2638306073747891</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01325917124942102</v>
+        <v>18.67856203578664</v>
       </c>
       <c r="E3" t="n">
-        <v>2.151606933843013</v>
+        <v>0.02397098387411416</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0783091834800308</v>
+        <v>0.03383814025109462</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2470733791131532</v>
+        <v>0.0216570995576821</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -2157,46 +2157,46 @@
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7075339758674855</v>
+        <v>0.7065761982381304</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7359454388140416</v>
+        <v>0.7358996227825925</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.166267395066876</v>
+        <v>1.040282834253536</v>
       </c>
       <c r="R3" t="n">
-        <v>0.761569966525819</v>
+        <v>0.7615699665062527</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1646396706102183</v>
+        <v>0.1452436575838593</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3999999945860802</v>
+        <v>0.3999999945778784</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3655521647927926</v>
+        <v>0.33004237700595</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1187676990613332</v>
+        <v>0.1115525974183797</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6703135537634592</v>
+        <v>0.6684314845326559</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1175251467546148</v>
+        <v>0.1132083947735417</v>
       </c>
       <c r="Y3" t="n">
-        <v>760243.8491079494</v>
+        <v>1886.463531825207</v>
       </c>
       <c r="Z3" t="n">
         <v>-1</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.7359454388140416</v>
+        <v>0.7358996227825925</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.761569966525819</v>
+        <v>0.7615699665062527</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -2207,66 +2207,66 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.6703135537634592</v>
+        <v>0.6684314845326559</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0552234488683037</v>
+        <v>0.2986783955302841</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.72408364673732e-06</v>
+        <v>0.0003543304565691389</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.310723987779651</v>
+        <v>0.01451836688553901</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.1174456015663288</v>
+        <v>0.05710803621085173</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.01255907900548735</v>
+        <v>0.00119222063763572</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.166267395066876</v>
+        <v>1.040282834253536</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1.328007276037948</v>
+        <v>-0.5786748227286269</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1.877483620203595</v>
+        <v>1.271343439133855</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.3327629351844993</v>
+        <v>-1.620314140253805</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1.10618730434266</v>
+        <v>-1.470593513862387</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.6071740450757601</v>
+        <v>-1.664399707010766</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0260300013176861</v>
+        <v>0.04698862362078716</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9334028457295769</v>
+        <v>0.01325917124942102</v>
       </c>
       <c r="E4" t="n">
-        <v>22.74354390023092</v>
+        <v>2.151606933843013</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3640585039483271</v>
+        <v>0.0783091834800308</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02867338561159859</v>
+        <v>0.2470733791131532</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -2290,46 +2290,46 @@
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7068416314792689</v>
+        <v>0.7075339758674855</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7362941207571385</v>
+        <v>0.7359454388140416</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.08876454754024</v>
+        <v>2.166267395066876</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7615699665295262</v>
+        <v>0.761569966525819</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1437270658663271</v>
+        <v>0.1646396706102183</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3999999949369086</v>
+        <v>0.3999999945860802</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3272833303301916</v>
+        <v>0.3655521647927926</v>
       </c>
       <c r="V4" t="n">
-        <v>0.110968669304937</v>
+        <v>0.1187676990613332</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6685628413596983</v>
+        <v>0.6703135537634592</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1128747143516319</v>
+        <v>0.1175251467546148</v>
       </c>
       <c r="Y4" t="n">
-        <v>449640.5474722028</v>
+        <v>760243.8491079494</v>
       </c>
       <c r="Z4" t="n">
         <v>-1</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.7362941207571385</v>
+        <v>0.7359454388140416</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7615699665295262</v>
+        <v>0.761569966525819</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -2340,43 +2340,309 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.6685628413596983</v>
+        <v>0.6703135537634592</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0293812896330642</v>
+        <v>0.0552234488683037</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.06217304349942e-05</v>
+        <v>1.72408364673732e-06</v>
       </c>
       <c r="AH4" t="n">
-        <v>13.76877163733701</v>
+        <v>1.310723987779651</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.6204284576181448</v>
+        <v>0.1174456015663288</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.001589699861886491</v>
+        <v>0.01255907900548735</v>
       </c>
       <c r="AK4" t="n">
-        <v>15.08876454754024</v>
+        <v>2.166267395066876</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
+        <v>-1.328007276037948</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-1.877483620203595</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.3327629351844993</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-1.10618730434266</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-0.6071740450757601</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.0260300013176861</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9334028457295769</v>
+      </c>
+      <c r="E5" t="n">
+        <v>22.74354390023092</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3640585039483271</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.02867338561159859</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.7068416316115292</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.7362941208846542</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>15.08876454814784</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.7615699665223312</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.1437270659696543</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.3999999946869297</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.3272833305199696</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.1109686700249502</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.6685628415435685</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.1128747143828861</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>449640.5812073005</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.7362941208846542</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.7615699665223312</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>robust</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.6685628415435685</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.02938128964119966</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.062172813939781e-05</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>13.76877163817078</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.6204284572027006</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.001589699861456285</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>15.08876454814784</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
         <v>-1.584525809905986</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AN5" t="n">
         <v>-0.02993087938533014</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AO5" t="n">
         <v>1.356858137414048</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AP5" t="n">
         <v>-0.4388288199215503</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AQ5" t="n">
         <v>-1.5425210246808</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.07969296261459534</v>
+      </c>
+      <c r="D6" t="n">
+        <v>68.02461780006593</v>
+      </c>
+      <c r="E6" t="n">
+        <v>11.62825144079468</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3879907805271877</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.467194524883676</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.7088706979372842</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.7371458387517306</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>8.511240240793912</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.7615699665206378</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.1723659449643951</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.3999999946667304</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.3726819935734484</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.1215225387248258</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.6717220663314228</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.1190519786978871</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1667.953888504739</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.7371458387517306</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.7615699665206378</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>robust</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.6717220663314228</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.09487604887564317</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.004255610848348133</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>7.098162662465219</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.5692803863700776</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.0729434659032015</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>8.511240240793912</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-1.098580027820818</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.832666110351999</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1.065514414065798</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-0.4111785940288324</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.1664876976762431</v>
       </c>
     </row>
   </sheetData>
@@ -2390,7 +2656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK4"/>
+  <dimension ref="A1:AK6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2585,7 +2851,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="C2" t="b">
         <v>1</v>
@@ -2594,19 +2860,19 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2638306073747891</v>
+        <v>0.2617924037677132</v>
       </c>
       <c r="F2" t="n">
-        <v>18.67856203578664</v>
+        <v>0.5063414494913574</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02397098387411416</v>
+        <v>0.1939218787159543</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03383814025109462</v>
+        <v>0.08419230020946894</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0216570995576821</v>
+        <v>0.6142627044519234</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -2621,76 +2887,76 @@
         <v>0.45</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7208494626215385</v>
+        <v>0.7444054599545181</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.8167931169621288</v>
+        <v>0.8387599304156891</v>
       </c>
       <c r="R2" t="n">
-        <v>1.040282834249715</v>
+        <v>2.285851010291753</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7615699665062574</v>
+        <v>0.7615699665167774</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1452436575720933</v>
+        <v>0.1788481995679346</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3999999945492236</v>
+        <v>0.3999999940328602</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3300423769804709</v>
+        <v>0.3489992374100511</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1115525974178364</v>
+        <v>0.202142601472262</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6684314845337777</v>
+        <v>1.650277339157503</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1132083947705028</v>
+        <v>0.1214009272121539</v>
       </c>
       <c r="Z2" t="n">
-        <v>1886.463542801643</v>
+        <v>432.6412857493505</v>
       </c>
       <c r="AA2" t="n">
         <v>-1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8167931169621288</v>
+        <v>0.8387599304156891</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7615699665062574</v>
+        <v>0.7615699665167774</v>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.6684314845337777</v>
+        <v>1.650277339157503</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2986783955222664</v>
+        <v>0.3178184055449895</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.0003543304545080528</v>
+        <v>0.003814424081832973</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.01451836688547894</v>
+        <v>0.1308574044833624</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.05710803621596595</v>
+        <v>0.1361832363263916</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.001192220637717448</v>
+        <v>0.04690020069767297</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.040282834249715</v>
+        <v>2.285851010291753</v>
       </c>
     </row>
     <row r="3">
@@ -2698,7 +2964,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="C3" t="b">
         <v>1</v>
@@ -2707,19 +2973,19 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04698862362078716</v>
+        <v>0.2638306073747891</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01325917124942102</v>
+        <v>18.67856203578664</v>
       </c>
       <c r="G3" t="n">
-        <v>2.151606933843013</v>
+        <v>0.02397098387411416</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0783091834800308</v>
+        <v>0.03383814025109462</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2470733791131532</v>
+        <v>0.0216570995576821</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -2734,76 +3000,76 @@
         <v>0.45</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7212198532620753</v>
+        <v>0.7601979348234716</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.8131152292092879</v>
+        <v>0.8575579987592914</v>
       </c>
       <c r="R3" t="n">
-        <v>2.166267395045595</v>
+        <v>2.134397497159925</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7615699665258173</v>
+        <v>0.732233030706118</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1646396705960972</v>
+        <v>0.184957182704297</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3999999944048857</v>
+        <v>0.3999999946171829</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3655521648352896</v>
+        <v>0.3539002424884955</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1187676990826549</v>
+        <v>0.1976472025380029</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6703135537658776</v>
+        <v>1.699757201667448</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1175251467514151</v>
+        <v>0.1209115021446534</v>
       </c>
       <c r="Z3" t="n">
-        <v>760243.8478594602</v>
+        <v>1025.360169492897</v>
       </c>
       <c r="AA3" t="n">
         <v>-1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8131152292092879</v>
+        <v>0.8575579987592914</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7615699665258173</v>
+        <v>0.732233030706118</v>
       </c>
       <c r="AD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.6703135537658776</v>
+        <v>1.699757201667448</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0552234488668002</v>
+        <v>0.3190015504942201</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.724083649561253e-06</v>
+        <v>0.04338139395991607</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.310723987774028</v>
+        <v>0.01670553972208854</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.1174456015503173</v>
+        <v>0.0538940941040578</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.01255907900492259</v>
+        <v>0.001657717212194893</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.166267395045595</v>
+        <v>2.134397497159925</v>
       </c>
     </row>
     <row r="4">
@@ -2811,7 +3077,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C4" t="b">
         <v>1</v>
@@ -2820,19 +3086,19 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0260300013176861</v>
+        <v>0.04698862362078716</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9334028457295769</v>
+        <v>0.01325917124942102</v>
       </c>
       <c r="G4" t="n">
-        <v>22.74354390023092</v>
+        <v>2.151606933843013</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3640585039483271</v>
+        <v>0.0783091834800308</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02867338561159859</v>
+        <v>0.2470733791131532</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -2853,70 +3119,296 @@
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7212002056733996</v>
+        <v>0.7212198531151057</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8177328782150537</v>
+        <v>0.8131152292079225</v>
       </c>
       <c r="R4" t="n">
-        <v>15.08876454739261</v>
+        <v>2.166267395059844</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7615699665295264</v>
+        <v>0.761569966525819</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1437270658530917</v>
+        <v>0.1646396706065065</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3999999947479901</v>
+        <v>0.3999999944802849</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3272833303686684</v>
+        <v>0.3655521648059379</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1109686693261145</v>
+        <v>0.1187676990756998</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6685628413624938</v>
+        <v>0.6703135537648173</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1128747143482263</v>
+        <v>0.117525146753172</v>
       </c>
       <c r="Z4" t="n">
-        <v>449640.5514221555</v>
+        <v>760243.8472732928</v>
       </c>
       <c r="AA4" t="n">
         <v>-1</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8177328782150537</v>
+        <v>0.8131152292079225</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7615699665295264</v>
+        <v>0.761569966525819</v>
       </c>
       <c r="AD4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.6703135537648173</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.05522344886762574</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.724083650894573e-06</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.310723987777075</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.1174456015613583</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.01255907900531688</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>2.166267395059844</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>29</v>
+      </c>
+      <c r="C5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.0260300013176861</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9334028457295769</v>
+      </c>
+      <c r="G5" t="n">
+        <v>22.74354390023092</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.3640585039483271</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.02867338561159859</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.7212002056599318</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.8177328782404792</v>
+      </c>
+      <c r="R5" t="n">
+        <v>15.08876454754707</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.7615699665275188</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.1437270658811942</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.3999999946546958</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.3272833304261334</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.1109686695300968</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.668562841414072</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.1128747143566728</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>449640.5616920041</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8177328782404792</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.7615699665275188</v>
+      </c>
+      <c r="AD5" t="b">
         <v>0</v>
       </c>
-      <c r="AE4" t="n">
-        <v>0.6685628413624938</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.02938128963217774</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3.062173016585083e-05</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>13.76877163727362</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0.6204284575323084</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0.001589699861842102</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>15.08876454739261</v>
+      <c r="AE5" t="n">
+        <v>0.668562841414072</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.02938128963437637</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.062172946695246e-05</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>13.7687716375011</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.6204284574063411</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.001589699861715438</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>15.08876454754707</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>20</v>
+      </c>
+      <c r="C6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.07969296261459534</v>
+      </c>
+      <c r="F6" t="n">
+        <v>68.02461780006593</v>
+      </c>
+      <c r="G6" t="n">
+        <v>11.62825144079468</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.3879907805271877</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.467194524883676</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>10</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.7224296045237203</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.8136870878707042</v>
+      </c>
+      <c r="R6" t="n">
+        <v>8.511240240379266</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.7615699665290998</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.1723659448680279</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.3999999946168681</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.3726819934022206</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.1215225378967506</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.6717220660930919</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.1190519786605096</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1667.953870709421</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8136870878707042</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.7615699665290998</v>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.6717220660930919</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.0948760488458559</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.004255610893452112</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>7.098162661966626</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.5692803866649987</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.07294346591524022</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>8.511240240379266</v>
       </c>
     </row>
   </sheetData>
@@ -2930,7 +3422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:S41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3043,7 +3535,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.040282843866633</v>
+        <v>1.253673765838883</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="b">
@@ -3051,40 +3543,40 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.8167931090546811</v>
+        <v>0.8130692319745823</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8167931090546811</v>
+        <v>0.8130692319745823</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8167931090546811</v>
+        <v>0.8130692319745823</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8167931090546811</v>
+        <v>0.8130692319745823</v>
       </c>
       <c r="L2" t="n">
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2638306073747891</v>
+        <v>0.2617924037677132</v>
       </c>
       <c r="P2" t="n">
-        <v>18.67856203578664</v>
+        <v>0.5063414494913574</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.02397098387411416</v>
+        <v>0.1939218787159543</v>
       </c>
       <c r="R2" t="n">
-        <v>0.03383814025109462</v>
+        <v>0.08419230020946894</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0216570995576821</v>
+        <v>0.6142627044519234</v>
       </c>
     </row>
     <row r="3">
@@ -3100,7 +3592,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.040282855687076</v>
+        <v>1.253673762700456</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="b">
@@ -3108,40 +3600,40 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.8167930967490119</v>
+        <v>0.8130692308907346</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8167930967490119</v>
+        <v>0.8130692308907346</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8167930967490119</v>
+        <v>0.8130692308907346</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8167930967490119</v>
+        <v>0.8130692308907346</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2638306073747891</v>
+        <v>0.2617924037677132</v>
       </c>
       <c r="P3" t="n">
-        <v>18.67856203578664</v>
+        <v>0.5063414494913574</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.02397098387411416</v>
+        <v>0.1939218787159543</v>
       </c>
       <c r="R3" t="n">
-        <v>0.03383814025109462</v>
+        <v>0.08419230020946894</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0216570995576821</v>
+        <v>0.6142627044519234</v>
       </c>
     </row>
     <row r="4">
@@ -3157,7 +3649,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.122912118065264</v>
+        <v>2.285851019517571</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="b">
@@ -3165,40 +3657,40 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.9718481796781019</v>
+        <v>0.8387599310036455</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9718481796781019</v>
+        <v>0.8387599310036455</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9718481796781019</v>
+        <v>0.8387599310036455</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9718481796781019</v>
+        <v>0.8387599310036455</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2638306073747891</v>
+        <v>0.2617924037677132</v>
       </c>
       <c r="P4" t="n">
-        <v>18.67856203578664</v>
+        <v>0.5063414494913574</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02397098387411416</v>
+        <v>0.1939218787159543</v>
       </c>
       <c r="R4" t="n">
-        <v>0.03383814025109462</v>
+        <v>0.08419230020946894</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0216570995576821</v>
+        <v>0.6142627044519234</v>
       </c>
     </row>
     <row r="5">
@@ -3210,54 +3702,52 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kept</t>
+          <t>dropped_by_dedup_or_rank</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.122912116367212</v>
+        <v>1.253673762264563</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.9718481752345759</v>
+        <v>0.8130692307418272</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9718481752345759</v>
+        <v>0.8130692307418272</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9718481752345759</v>
+        <v>0.8130692307418272</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9718481752345759</v>
+        <v>0.8130692307418272</v>
       </c>
       <c r="L5" t="n">
         <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="N5" t="n">
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2638306073747891</v>
+        <v>0.2617924037677132</v>
       </c>
       <c r="P5" t="n">
-        <v>18.67856203578664</v>
+        <v>0.5063414494913574</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02397098387411416</v>
+        <v>0.1939218787159543</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03383814025109462</v>
+        <v>0.08419230020946894</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0216570995576821</v>
+        <v>0.6142627044519234</v>
       </c>
     </row>
     <row r="6">
@@ -3273,7 +3763,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.040282834594009</v>
+        <v>2.285851041262932</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="b">
@@ -3281,40 +3771,40 @@
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.8167931166869666</v>
+        <v>0.8387599324606982</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8167931166869666</v>
+        <v>0.8387599324606982</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8167931166869666</v>
+        <v>0.8387599324606982</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8167931166869666</v>
+        <v>0.8387599324606982</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="N6" t="n">
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2638306073747891</v>
+        <v>0.2617924037677132</v>
       </c>
       <c r="P6" t="n">
-        <v>18.67856203578664</v>
+        <v>0.5063414494913574</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.02397098387411416</v>
+        <v>0.1939218787159543</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03383814025109462</v>
+        <v>0.08419230020946894</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0216570995576821</v>
+        <v>0.6142627044519234</v>
       </c>
     </row>
     <row r="7">
@@ -3330,7 +3820,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.040282834249715</v>
+        <v>1.253673761621897</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="b">
@@ -3340,334 +3830,336 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8167931169621288</v>
+        <v>0.9537329091153749</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8167931169621288</v>
+        <v>0.9537329091153749</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8167931169621288</v>
+        <v>0.9537329091153749</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8167931169621288</v>
+        <v>0.9537329091153749</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="N7" t="n">
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2638306073747891</v>
+        <v>0.2617924037677132</v>
       </c>
       <c r="P7" t="n">
-        <v>18.67856203578664</v>
+        <v>0.5063414494913574</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.02397098387411416</v>
+        <v>0.1939218787159543</v>
       </c>
       <c r="R7" t="n">
-        <v>0.03383814025109462</v>
+        <v>0.08419230020946894</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0216570995576821</v>
+        <v>0.6142627044519234</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B8" t="b">
         <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dropped_by_dedup_or_rank</t>
+          <t>kept</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2.166267395066876</v>
+        <v>2.285851010291753</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
       <c r="H8" t="n">
-        <v>0.8131152292084022</v>
+        <v>0.8387599304156891</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8131152292084022</v>
+        <v>0.8387599304156891</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8131152292084022</v>
+        <v>0.8387599304156891</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8131152292084022</v>
+        <v>0.8387599304156891</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>0.04698862362078716</v>
+        <v>0.2617924037677132</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01325917124942102</v>
+        <v>0.5063414494913574</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.151606933843013</v>
+        <v>0.1939218787159543</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0783091834800308</v>
+        <v>0.08419230020946894</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2470733791131532</v>
+        <v>0.6142627044519234</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B9" t="b">
         <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kept</t>
+          <t>dropped_by_dedup_or_rank</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3.304741084494661</v>
+        <v>2.285851010846894</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>0.8387444989570139</v>
+        <v>0.8387599304082214</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8387444989570139</v>
+        <v>0.8387599304082214</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8387444989570139</v>
+        <v>0.8387599304082214</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8387444989570139</v>
+        <v>0.8387599304082214</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="N9" t="n">
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04698862362078716</v>
+        <v>0.2617924037677132</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01325917124942102</v>
+        <v>0.5063414494913574</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.151606933843013</v>
+        <v>0.1939218787159543</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0783091834800308</v>
+        <v>0.08419230020946894</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2470733791131532</v>
+        <v>0.6142627044519234</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B10" t="b">
         <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>kept</t>
+          <t>dropped_by_dedup_or_rank</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2.166267395045595</v>
+        <v>1.040282843866633</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>0.8131152292092879</v>
+        <v>0.8167931090546811</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8131152292092879</v>
+        <v>0.8167931090546811</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8131152292092879</v>
+        <v>0.8167931090546811</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8131152292092879</v>
+        <v>0.8167931090546811</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04698862362078716</v>
+        <v>0.2638306073747891</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01325917124942102</v>
+        <v>18.67856203578664</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.151606933843013</v>
+        <v>0.02397098387411416</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0783091834800308</v>
+        <v>0.03383814025109462</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2470733791131532</v>
+        <v>0.0216570995576821</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B11" t="b">
         <v>1</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dropped_by_dedup_or_rank</t>
+          <t>kept</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3.304741084820124</v>
+        <v>2.134397497159925</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
       <c r="H11" t="n">
-        <v>0.8387444989552623</v>
+        <v>0.8575579987592914</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8387444989552623</v>
+        <v>0.8575579987592914</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8387444989552623</v>
+        <v>0.8575579987592914</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8387444989552623</v>
+        <v>0.8575579987592914</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>0.04698862362078716</v>
+        <v>0.2638306073747891</v>
       </c>
       <c r="P11" t="n">
-        <v>0.01325917124942102</v>
+        <v>18.67856203578664</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.151606933843013</v>
+        <v>0.02397098387411416</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0783091834800308</v>
+        <v>0.03383814025109462</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2470733791131532</v>
+        <v>0.0216570995576821</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B12" t="b">
         <v>1</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dropped_by_dedup_or_rank</t>
+          <t>kept</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2.166267397495013</v>
+        <v>1.040282834242392</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
       <c r="H12" t="n">
-        <v>0.8131152296562263</v>
+        <v>0.8167931169597799</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8131152296562263</v>
+        <v>0.8167931169597799</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8131152296562263</v>
+        <v>0.8167931169597799</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8131152296562263</v>
+        <v>0.8167931169597799</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="N12" t="n">
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>0.04698862362078716</v>
+        <v>0.2638306073747891</v>
       </c>
       <c r="P12" t="n">
-        <v>0.01325917124942102</v>
+        <v>18.67856203578664</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.151606933843013</v>
+        <v>0.02397098387411416</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0783091834800308</v>
+        <v>0.03383814025109462</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2470733791131532</v>
+        <v>0.0216570995576821</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B13" t="b">
         <v>1</v>
@@ -3678,7 +4170,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3.304741084695373</v>
+        <v>1.040282835162699</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="b">
@@ -3686,102 +4178,104 @@
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.8387444989557274</v>
+        <v>0.8167931163836201</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8387444989557274</v>
+        <v>0.8167931163836201</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8387444989557274</v>
+        <v>0.8167931163836201</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8387444989557274</v>
+        <v>0.8167931163836201</v>
       </c>
       <c r="L13" t="n">
         <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.04698862362078716</v>
+        <v>0.2638306073747891</v>
       </c>
       <c r="P13" t="n">
-        <v>0.01325917124942102</v>
+        <v>18.67856203578664</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.151606933843013</v>
+        <v>0.02397098387411416</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0783091834800308</v>
+        <v>0.03383814025109462</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2470733791131532</v>
+        <v>0.0216570995576821</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B14" t="b">
         <v>1</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dropped_by_dedup_or_rank</t>
+          <t>kept</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.08876456223531</v>
+        <v>1.122912116862486</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
       <c r="H14" t="n">
-        <v>0.8177328795250973</v>
+        <v>0.9718481765600018</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8177328795250973</v>
+        <v>0.9718481765600018</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8177328795250973</v>
+        <v>0.9718481765600018</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8177328795250973</v>
+        <v>0.9718481765600018</v>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0260300013176861</v>
+        <v>0.2638306073747891</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9334028457295769</v>
+        <v>18.67856203578664</v>
       </c>
       <c r="Q14" t="n">
-        <v>22.74354390023092</v>
+        <v>0.02397098387411416</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3640585039483271</v>
+        <v>0.03383814025109462</v>
       </c>
       <c r="S14" t="n">
-        <v>0.02867338561159859</v>
+        <v>0.0216570995576821</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B15" t="b">
         <v>1</v>
@@ -3792,7 +4286,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.0887645499136</v>
+        <v>2.134397511558196</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="b">
@@ -3800,45 +4294,45 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.8177328785019731</v>
+        <v>0.8575579920711986</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8177328785019731</v>
+        <v>0.8575579920711986</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8177328785019731</v>
+        <v>0.8575579920711986</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8177328785019731</v>
+        <v>0.8575579920711986</v>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="N15" t="n">
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0260300013176861</v>
+        <v>0.2638306073747891</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9334028457295769</v>
+        <v>18.67856203578664</v>
       </c>
       <c r="Q15" t="n">
-        <v>22.74354390023092</v>
+        <v>0.02397098387411416</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3640585039483271</v>
+        <v>0.03383814025109462</v>
       </c>
       <c r="S15" t="n">
-        <v>0.02867338561159859</v>
+        <v>0.0216570995576821</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B16" t="b">
         <v>1</v>
@@ -3849,7 +4343,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.0887645554218</v>
+        <v>1.040282835728531</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="b">
@@ -3857,45 +4351,45 @@
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.8177328791549391</v>
+        <v>0.8167931163988011</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8177328791549391</v>
+        <v>0.8167931163988011</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8177328791549391</v>
+        <v>0.8167931163988011</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8177328791549391</v>
+        <v>0.8167931163988011</v>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="N16" t="n">
         <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0260300013176861</v>
+        <v>0.2638306073747891</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9334028457295769</v>
+        <v>18.67856203578664</v>
       </c>
       <c r="Q16" t="n">
-        <v>22.74354390023092</v>
+        <v>0.02397098387411416</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3640585039483271</v>
+        <v>0.03383814025109462</v>
       </c>
       <c r="S16" t="n">
-        <v>0.02867338561159859</v>
+        <v>0.0216570995576821</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B17" t="b">
         <v>1</v>
@@ -3906,7 +4400,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.08876454873163</v>
+        <v>1.040282834259724</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="b">
@@ -3914,156 +4408,1412 @@
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.8177328782689758</v>
+        <v>0.8167931169546175</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8177328782689758</v>
+        <v>0.8167931169546175</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8177328782689758</v>
+        <v>0.8167931169546175</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8177328782689758</v>
+        <v>0.8167931169546175</v>
       </c>
       <c r="L17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0260300013176861</v>
+        <v>0.2638306073747891</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9334028457295769</v>
+        <v>18.67856203578664</v>
       </c>
       <c r="Q17" t="n">
-        <v>22.74354390023092</v>
+        <v>0.02397098387411416</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3640585039483271</v>
+        <v>0.03383814025109462</v>
       </c>
       <c r="S17" t="n">
-        <v>0.02867338561159859</v>
+        <v>0.0216570995576821</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B18" t="b">
         <v>1</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>kept</t>
+          <t>dropped_by_dedup_or_rank</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.08876454739261</v>
+        <v>2.166267395066876</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>0.8177328782150537</v>
+        <v>0.8131152292084022</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8177328782150537</v>
+        <v>0.8131152292084022</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8177328782150537</v>
+        <v>0.8131152292084022</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8177328782150537</v>
+        <v>0.8131152292084022</v>
       </c>
       <c r="L18" t="n">
         <v>3</v>
       </c>
       <c r="M18" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N18" t="n">
         <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0260300013176861</v>
+        <v>0.04698862362078716</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9334028457295769</v>
+        <v>0.01325917124942102</v>
       </c>
       <c r="Q18" t="n">
-        <v>22.74354390023092</v>
+        <v>2.151606933843013</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3640585039483271</v>
+        <v>0.0783091834800308</v>
       </c>
       <c r="S18" t="n">
-        <v>0.02867338561159859</v>
+        <v>0.2470733791131532</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B19" t="b">
         <v>1</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dropped_by_dedup_or_rank</t>
+          <t>kept</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.08876454818332</v>
+        <v>2.166267395059844</v>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
       <c r="H19" t="n">
-        <v>0.8177328783037147</v>
+        <v>0.8131152292079225</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8177328783037147</v>
+        <v>0.8131152292079225</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8177328783037147</v>
+        <v>0.8131152292079225</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8177328783037147</v>
+        <v>0.8131152292079225</v>
       </c>
       <c r="L19" t="n">
         <v>3</v>
       </c>
       <c r="M19" t="n">
+        <v>27</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.04698862362078716</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.01325917124942102</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.151606933843013</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.0783091834800308</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.2470733791131532</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" t="b">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>dropped_by_dedup_or_rank</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2.16626739507475</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="n">
+        <v>0.8131152292073038</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8131152292073038</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.8131152292073038</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.8131152292073038</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3</v>
+      </c>
+      <c r="M20" t="n">
+        <v>27</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.04698862362078716</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.01325917124942102</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.151606933843013</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.0783091834800308</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.2470733791131532</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" t="b">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>dropped_by_dedup_or_rank</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2.166267397648115</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>0.8131152297235159</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.8131152297235159</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.8131152297235159</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.8131152297235159</v>
+      </c>
+      <c r="L21" t="n">
+        <v>3</v>
+      </c>
+      <c r="M21" t="n">
+        <v>27</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.04698862362078716</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.01325917124942102</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.151606933843013</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.0783091834800308</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.2470733791131532</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" t="b">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>dropped_by_dedup_or_rank</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2.166267395098269</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>0.8131152292059001</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.8131152292059001</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.8131152292059001</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.8131152292059001</v>
+      </c>
+      <c r="L22" t="n">
+        <v>3</v>
+      </c>
+      <c r="M22" t="n">
+        <v>27</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.04698862362078716</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.01325917124942102</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.151606933843013</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.0783091834800308</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.2470733791131532</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" t="b">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>dropped_by_dedup_or_rank</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2.166267395169136</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="n">
+        <v>0.8131152292185194</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.8131152292185194</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.8131152292185194</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.8131152292185194</v>
+      </c>
+      <c r="L23" t="n">
+        <v>3</v>
+      </c>
+      <c r="M23" t="n">
+        <v>27</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.04698862362078716</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.01325917124942102</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.151606933843013</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.0783091834800308</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.2470733791131532</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>7</v>
+      </c>
+      <c r="B24" t="b">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>dropped_by_dedup_or_rank</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2.166267395137878</v>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>0.8131152292185257</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.8131152292185257</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.8131152292185257</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.8131152292185257</v>
+      </c>
+      <c r="L24" t="n">
+        <v>3</v>
+      </c>
+      <c r="M24" t="n">
+        <v>27</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.04698862362078716</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.01325917124942102</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.151606933843013</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.0783091834800308</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.2470733791131532</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>8</v>
+      </c>
+      <c r="B25" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Error in Opti::solve [OptiNode] at .../casadi/core/optistack.cpp:217:
+.../casadi/core/optistack_internal.cpp:1338: Assertion "return_success(accept_limit)" failed:
+Solver failed. You may use opti.debug.value to investigate the latest values of variables. return_status is 'Infeasible_Problem_Detected'</t>
+        </is>
+      </c>
+      <c r="F25" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>3</v>
+      </c>
+      <c r="M25" t="n">
+        <v>27</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.04698862362078716</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.01325917124942102</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.151606933843013</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.0783091834800308</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.2470733791131532</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" t="b">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>dropped_by_dedup_or_rank</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>15.08876456223531</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="n">
+        <v>0.8177328795250973</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8177328795250973</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.8177328795250973</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.8177328795250973</v>
+      </c>
+      <c r="L26" t="n">
+        <v>4</v>
+      </c>
+      <c r="M26" t="n">
         <v>29</v>
       </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="n">
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" t="n">
         <v>0.0260300013176861</v>
       </c>
-      <c r="P19" t="n">
+      <c r="P26" t="n">
         <v>0.9334028457295769</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="Q26" t="n">
         <v>22.74354390023092</v>
       </c>
-      <c r="R19" t="n">
+      <c r="R26" t="n">
         <v>0.3640585039483271</v>
       </c>
-      <c r="S19" t="n">
+      <c r="S26" t="n">
         <v>0.02867338561159859</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B27" t="b">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>dropped_by_dedup_or_rank</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>15.08876456376025</v>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="n">
+        <v>0.8177328800449281</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.8177328800449281</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.8177328800449281</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.8177328800449281</v>
+      </c>
+      <c r="L27" t="n">
+        <v>4</v>
+      </c>
+      <c r="M27" t="n">
+        <v>29</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.0260300013176861</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.9334028457295769</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>22.74354390023092</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.3640585039483271</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.02867338561159859</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" t="b">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>dropped_by_dedup_or_rank</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>15.08876454924798</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="b">
+        <v>0</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>0.8177328784263462</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.8177328784263462</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.8177328784263462</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.8177328784263462</v>
+      </c>
+      <c r="L28" t="n">
+        <v>4</v>
+      </c>
+      <c r="M28" t="n">
+        <v>29</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.0260300013176861</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.9334028457295769</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>22.74354390023092</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.3640585039483271</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.02867338561159859</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B29" t="b">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>dropped_by_dedup_or_rank</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>15.08876454771134</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="b">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>0.8177328782464313</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.8177328782464313</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.8177328782464313</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.8177328782464313</v>
+      </c>
+      <c r="L29" t="n">
+        <v>4</v>
+      </c>
+      <c r="M29" t="n">
+        <v>29</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.0260300013176861</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.9334028457295769</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>22.74354390023092</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.3640585039483271</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.02867338561159859</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>5</v>
+      </c>
+      <c r="B30" t="b">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>kept</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>15.08876454754707</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.8177328782404792</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.8177328782404792</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.8177328782404792</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.8177328782404792</v>
+      </c>
+      <c r="L30" t="n">
+        <v>4</v>
+      </c>
+      <c r="M30" t="n">
+        <v>29</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.0260300013176861</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.9334028457295769</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>22.74354390023092</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.3640585039483271</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.02867338561159859</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>6</v>
+      </c>
+      <c r="B31" t="b">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>kept</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>15.75508933133658</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.8594713976120751</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.8594713976120751</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.8594713976120751</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.8594713976120751</v>
+      </c>
+      <c r="L31" t="n">
+        <v>4</v>
+      </c>
+      <c r="M31" t="n">
+        <v>29</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.0260300013176861</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.9334028457295769</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>22.74354390023092</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.3640585039483271</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.02867338561159859</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>7</v>
+      </c>
+      <c r="B32" t="b">
+        <v>1</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>kept</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>15.1735494642935</v>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.9801999076682432</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9801999076682432</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.9801999076682432</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.9801999076682432</v>
+      </c>
+      <c r="L32" t="n">
+        <v>4</v>
+      </c>
+      <c r="M32" t="n">
+        <v>29</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.0260300013176861</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.9334028457295769</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>22.74354390023092</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.3640585039483271</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.02867338561159859</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>8</v>
+      </c>
+      <c r="B33" t="b">
+        <v>0</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Error in Opti::solve [OptiNode] at .../casadi/core/optistack.cpp:217:
+.../casadi/core/optistack_internal.cpp:1338: Assertion "return_success(accept_limit)" failed:
+Solver failed. You may use opti.debug.value to investigate the latest values of variables. return_status is 'Infeasible_Problem_Detected'</t>
+        </is>
+      </c>
+      <c r="F33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>4</v>
+      </c>
+      <c r="M33" t="n">
+        <v>29</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.0260300013176861</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.9334028457295769</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>22.74354390023092</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.3640585039483271</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.02867338561159859</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1</v>
+      </c>
+      <c r="B34" t="b">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>dropped_by_dedup_or_rank</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>8.511240248161135</v>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="b">
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="n">
+        <v>0.8136870911069487</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.8136870911069487</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.8136870911069487</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.8136870911069487</v>
+      </c>
+      <c r="L34" t="n">
+        <v>5</v>
+      </c>
+      <c r="M34" t="n">
+        <v>20</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.07969296261459534</v>
+      </c>
+      <c r="P34" t="n">
+        <v>68.02461780006593</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>11.62825144079468</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.3879907805271877</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1.467194524883676</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" t="b">
+        <v>1</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>dropped_by_dedup_or_rank</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>8.511240241650539</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="b">
+        <v>0</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="n">
+        <v>0.8136870884231152</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.8136870884231152</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.8136870884231152</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.8136870884231152</v>
+      </c>
+      <c r="L35" t="n">
+        <v>5</v>
+      </c>
+      <c r="M35" t="n">
+        <v>20</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.07969296261459534</v>
+      </c>
+      <c r="P35" t="n">
+        <v>68.02461780006593</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>11.62825144079468</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.3879907805271877</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.467194524883676</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>3</v>
+      </c>
+      <c r="B36" t="b">
+        <v>1</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>kept</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>9.050982377218075</v>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.858176570289341</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.858176570289341</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.858176570289341</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.858176570289341</v>
+      </c>
+      <c r="L36" t="n">
+        <v>5</v>
+      </c>
+      <c r="M36" t="n">
+        <v>20</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.07969296261459534</v>
+      </c>
+      <c r="P36" t="n">
+        <v>68.02461780006593</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>11.62825144079468</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.3879907805271877</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1.467194524883676</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>4</v>
+      </c>
+      <c r="B37" t="b">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>dropped_by_dedup_or_rank</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>8.511240240431476</v>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="b">
+        <v>0</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="n">
+        <v>0.813687087870468</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.813687087870468</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.813687087870468</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.813687087870468</v>
+      </c>
+      <c r="L37" t="n">
+        <v>5</v>
+      </c>
+      <c r="M37" t="n">
+        <v>20</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.07969296261459534</v>
+      </c>
+      <c r="P37" t="n">
+        <v>68.02461780006593</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>11.62825144079468</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.3879907805271877</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1.467194524883676</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>5</v>
+      </c>
+      <c r="B38" t="b">
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>dropped_by_dedup_or_rank</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>8.511240243189246</v>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="b">
+        <v>0</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="n">
+        <v>0.8136870889881901</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.8136870889881901</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.8136870889881901</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.8136870889881901</v>
+      </c>
+      <c r="L38" t="n">
+        <v>5</v>
+      </c>
+      <c r="M38" t="n">
+        <v>20</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.07969296261459534</v>
+      </c>
+      <c r="P38" t="n">
+        <v>68.02461780006593</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>11.62825144079468</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.3879907805271877</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1.467194524883676</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>6</v>
+      </c>
+      <c r="B39" t="b">
+        <v>1</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>dropped_by_dedup_or_rank</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>8.511240241776694</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="b">
+        <v>0</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="n">
+        <v>0.8136870884421271</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.8136870884421271</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.8136870884421271</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.8136870884421271</v>
+      </c>
+      <c r="L39" t="n">
+        <v>5</v>
+      </c>
+      <c r="M39" t="n">
+        <v>20</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.07969296261459534</v>
+      </c>
+      <c r="P39" t="n">
+        <v>68.02461780006593</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>11.62825144079468</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.3879907805271877</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1.467194524883676</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>7</v>
+      </c>
+      <c r="B40" t="b">
+        <v>1</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>dropped_by_dedup_or_rank</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>8.511240250605956</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="b">
+        <v>0</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="n">
+        <v>0.813687092020308</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.813687092020308</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.813687092020308</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.813687092020308</v>
+      </c>
+      <c r="L40" t="n">
+        <v>5</v>
+      </c>
+      <c r="M40" t="n">
+        <v>20</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.07969296261459534</v>
+      </c>
+      <c r="P40" t="n">
+        <v>68.02461780006593</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>11.62825144079468</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.3879907805271877</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1.467194524883676</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>8</v>
+      </c>
+      <c r="B41" t="b">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>kept</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>8.511240240379266</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.8136870878707042</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.8136870878707042</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.8136870878707042</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.8136870878707042</v>
+      </c>
+      <c r="L41" t="n">
+        <v>5</v>
+      </c>
+      <c r="M41" t="n">
+        <v>20</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.07969296261459534</v>
+      </c>
+      <c r="P41" t="n">
+        <v>68.02461780006593</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>11.62825144079468</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.3879907805271877</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1.467194524883676</v>
       </c>
     </row>
   </sheetData>
